--- a/data/trans_bre/P34A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,41; 22,75</t>
+          <t>11,52; 22,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 18,91</t>
+          <t>7,59; 18,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 25,28</t>
+          <t>13,13; 25,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 31,95</t>
+          <t>11,26; 31,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,83; 100,33</t>
+          <t>40,16; 100,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,22; 141,57</t>
+          <t>41,54; 143,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,74; 153,95</t>
+          <t>57,54; 158,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,56; 335,88</t>
+          <t>49,46; 320,62</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 13,15</t>
+          <t>3,39; 14,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 12,96</t>
+          <t>3,43; 13,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 15,56</t>
+          <t>5,07; 15,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 5,39</t>
+          <t>-18,03; 5,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 38,83</t>
+          <t>8,8; 44,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 74,42</t>
+          <t>16,87; 75,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,15; 65,06</t>
+          <t>17,24; 65,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 15,33</t>
+          <t>-44,63; 15,81</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 6,22</t>
+          <t>-5,3; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 8,09</t>
+          <t>-1,16; 8,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 4,96</t>
+          <t>-5,72; 5,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,0</t>
+          <t>-1,12; 10,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 15,36</t>
+          <t>-11,44; 14,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 35,04</t>
+          <t>-4,38; 37,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 15,44</t>
+          <t>-15,14; 15,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 32,06</t>
+          <t>-3,29; 33,75</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 1,53</t>
+          <t>-12,29; 0,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 8,99</t>
+          <t>-2,12; 8,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,53</t>
+          <t>-6,05; 5,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 30,39</t>
+          <t>0,96; 33,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 3,24</t>
+          <t>-22,77; 1,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 39,62</t>
+          <t>-7,86; 37,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 15,88</t>
+          <t>-14,6; 15,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 257,93</t>
+          <t>2,73; 252,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 0,65</t>
+          <t>-13,78; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,85</t>
+          <t>-4,84; 6,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 17,33</t>
+          <t>4,02; 16,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 3,47</t>
+          <t>-7,01; 3,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 1,56</t>
+          <t>-25,13; 2,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 33,02</t>
+          <t>-17,76; 32,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,6; 53,85</t>
+          <t>10,28; 50,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 9,48</t>
+          <t>-16,23; 9,17</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 16,98</t>
+          <t>1,45; 16,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,83; 18,97</t>
+          <t>4,22; 17,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 15,19</t>
+          <t>1,44; 16,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 7,66</t>
+          <t>-25,04; 7,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 49,22</t>
+          <t>3,37; 48,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,67; 111,69</t>
+          <t>15,84; 100,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 45,03</t>
+          <t>3,48; 48,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 25,36</t>
+          <t>-70,11; 23,58</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,19</t>
+          <t>2,03; 20,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,03; 30,77</t>
+          <t>15,5; 31,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,59; 25,01</t>
+          <t>9,17; 24,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,64; 27,36</t>
+          <t>16,0; 27,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 45,61</t>
+          <t>3,37; 45,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,39; 135,64</t>
+          <t>47,27; 139,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,48; 53,46</t>
+          <t>17,05; 53,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,69; 73,82</t>
+          <t>35,05; 73,76</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,49</t>
+          <t>2,65; 7,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,55</t>
+          <t>6,21; 10,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,18</t>
+          <t>6,51; 11,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 14,16</t>
+          <t>0,84; 13,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,72</t>
+          <t>6,23; 18,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,35; 49,77</t>
+          <t>26,13; 50,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,7; 34,37</t>
+          <t>18,62; 35,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 54,42</t>
+          <t>3,31; 52,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P34A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,3</t>
+          <t>22,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>154,42%</t>
+          <t>163,1%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 22,74</t>
+          <t>11,3; 23,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 18,72</t>
+          <t>8,07; 19,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,13; 25,71</t>
+          <t>12,82; 25,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 31,39</t>
+          <t>12,73; 30,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,16; 100,75</t>
+          <t>38,82; 104,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,54; 143,14</t>
+          <t>43,48; 145,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,54; 158,88</t>
+          <t>56,26; 155,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,46; 320,62</t>
+          <t>68,58; 315,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-8,46%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 14,43</t>
+          <t>3,43; 14,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 13,04</t>
+          <t>3,71; 13,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 15,52</t>
+          <t>5,06; 15,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 5,25</t>
+          <t>-3,25; 11,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 44,36</t>
+          <t>9,05; 43,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,87; 75,64</t>
+          <t>16,39; 78,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 65,71</t>
+          <t>17,81; 66,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 15,81</t>
+          <t>-8,54; 37,33</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 5,92</t>
+          <t>-5,26; 5,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 8,53</t>
+          <t>-1,53; 8,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 5,12</t>
+          <t>-5,85; 4,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 10,56</t>
+          <t>-1,39; 8,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 14,66</t>
+          <t>-11,46; 14,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 37,35</t>
+          <t>-5,38; 36,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 15,87</t>
+          <t>-15,69; 13,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 33,75</t>
+          <t>-3,14; 27,29</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,25</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>-1,39%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 0,91</t>
+          <t>-12,12; 1,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 8,25</t>
+          <t>-2,07; 8,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 5,54</t>
+          <t>-6,01; 5,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 33,18</t>
+          <t>-5,41; 4,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 1,95</t>
+          <t>-23,26; 2,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 37,51</t>
+          <t>-7,26; 39,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 15,51</t>
+          <t>-14,59; 14,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 252,31</t>
+          <t>-13,79; 12,46</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-2,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-4,16%</t>
+          <t>-5,2%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 0,97</t>
+          <t>-13,67; -0,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 6,92</t>
+          <t>-4,7; 7,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 16,43</t>
+          <t>3,9; 16,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,32</t>
+          <t>-6,82; 2,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 2,02</t>
+          <t>-25,85; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 32,65</t>
+          <t>-17,53; 32,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 50,39</t>
+          <t>9,79; 52,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 9,17</t>
+          <t>-16,04; 7,78</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,7</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-21,48%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 16,66</t>
+          <t>1,16; 16,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,22; 17,95</t>
+          <t>4,05; 18,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 16,25</t>
+          <t>0,11; 15,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 7,26</t>
+          <t>0,17; 10,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 48,25</t>
+          <t>1,78; 47,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,84; 100,81</t>
+          <t>15,69; 106,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 48,06</t>
+          <t>0,28; 43,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,11; 23,58</t>
+          <t>0,64; 38,35</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,61</t>
+          <t>21,77</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 20,02</t>
+          <t>2,47; 20,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,5; 31,72</t>
+          <t>14,97; 32,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 24,8</t>
+          <t>9,86; 24,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,0; 27,29</t>
+          <t>16,24; 27,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 45,03</t>
+          <t>4,3; 45,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,27; 139,58</t>
+          <t>46,54; 141,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,05; 53,57</t>
+          <t>18,54; 53,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,05; 73,76</t>
+          <t>35,71; 73,98</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,45</t>
+          <t>2,44; 7,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,68</t>
+          <t>6,25; 10,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,37</t>
+          <t>6,48; 11,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 13,63</t>
+          <t>4,98; 9,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,23; 18,6</t>
+          <t>5,71; 18,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,13; 50,2</t>
+          <t>26,67; 49,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,62; 35,42</t>
+          <t>18,58; 34,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,31; 52,15</t>
+          <t>14,15; 29,71</t>
         </is>
       </c>
     </row>
